--- a/data/trans_orig/P36BPD13_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P36BPD13_2023-Edad-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si consumen preferentemente carne de pollo, pavo o conejo en vez de ternera, cerdo, hamburguesas o salchichas en 2023</t>
+          <t>Población según si consumen preferentemente carne de pollo, pavo o conejo en vez de ternera, cerdo, hamburguesas o salchichas en 2023 (tasa de respuesta: 99,31%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>323733</t>
+          <t>321706</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>367965</t>
+          <t>369614</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>80,94%</t>
+          <t>80,43%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>91,99%</t>
+          <t>92,41%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>249034</t>
+          <t>248129</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>280839</t>
+          <t>281876</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>80,56%</t>
+          <t>80,27%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>90,85%</t>
+          <t>91,19%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>583934</t>
+          <t>587692</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>640649</t>
+          <t>641183</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>82,35%</t>
+          <t>82,88%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>90,35%</t>
+          <t>90,42%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>32022</t>
+          <t>30373</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>76254</t>
+          <t>78281</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>19,57%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>28277</t>
+          <t>27240</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>60082</t>
+          <t>60987</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>19,44%</t>
+          <t>19,73%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>68454</t>
+          <t>67920</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>125169</t>
+          <t>121411</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>17,12%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>319181</t>
+          <t>319121</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>363003</t>
+          <t>362181</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>75,63%</t>
+          <t>75,62%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>86,02%</t>
+          <t>85,82%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>442738</t>
+          <t>442921</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>477622</t>
+          <t>479024</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>87,7%</t>
+          <t>87,74%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>94,61%</t>
+          <t>94,89%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>771506</t>
+          <t>773107</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>833751</t>
+          <t>834646</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>83,24%</t>
+          <t>83,41%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>89,96%</t>
+          <t>90,05%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>59013</t>
+          <t>59835</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>102835</t>
+          <t>102895</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>14,18%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>24,37%</t>
+          <t>24,38%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>27208</t>
+          <t>25806</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>62092</t>
+          <t>61909</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>12,26%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>93095</t>
+          <t>92200</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>155340</t>
+          <t>153739</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>9,95%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>16,76%</t>
+          <t>16,59%</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>435283</t>
+          <t>436954</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>471007</t>
+          <t>472230</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,49 +1431,49 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>81,61%</t>
+          <t>81,92%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
+          <t>88,54%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>727</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>463729</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>448413</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>476843</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>85,88%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>83,04%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
           <t>88,31%</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>727</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>463729</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>447089</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>475799</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>85,88%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>82,8%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>88,11%</t>
-        </is>
-      </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>1201</t>
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>896261</t>
+          <t>897888</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>939702</t>
+          <t>942716</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>83,5%</t>
+          <t>83,65%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>87,55%</t>
+          <t>87,83%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>62361</t>
+          <t>61138</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>98085</t>
+          <t>96414</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,47 +1544,47 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
+          <t>11,46%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>18,08%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>76262</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>63148</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>91578</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>14,12%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
           <t>11,69%</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>18,39%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>115</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>76262</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>64192</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>92902</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>14,12%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>11,89%</t>
-        </is>
-      </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>16,96%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>133657</t>
+          <t>130643</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>177098</t>
+          <t>175471</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>12,17%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>16,5%</t>
+          <t>16,35%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>745475</t>
+          <t>743093</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>843794</t>
+          <t>844937</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>84,41%</t>
+          <t>84,14%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>95,54%</t>
+          <t>95,67%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>604962</t>
+          <t>604485</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>637708</t>
+          <t>637243</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>85,71%</t>
+          <t>85,64%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>90,35%</t>
+          <t>90,28%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1364307</t>
+          <t>1365074</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1477900</t>
+          <t>1478491</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>85,86%</t>
+          <t>85,91%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>93,01%</t>
+          <t>93,04%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>39410</t>
+          <t>38267</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>137729</t>
+          <t>140111</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>15,59%</t>
+          <t>15,86%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>68125</t>
+          <t>68590</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>100871</t>
+          <t>101348</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,72%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>14,29%</t>
+          <t>14,36%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>111137</t>
+          <t>110546</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>224730</t>
+          <t>223963</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>14,14%</t>
+          <t>14,09%</t>
         </is>
       </c>
     </row>
@@ -2102,12 +2102,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>427926</t>
+          <t>428202</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>464956</t>
+          <t>464848</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,12 +2117,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>76,87%</t>
+          <t>76,92%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>83,53%</t>
+          <t>83,51%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>467924</t>
+          <t>466801</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>491058</t>
+          <t>490295</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,12 +2152,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>85,61%</t>
+          <t>85,4%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>89,84%</t>
+          <t>89,7%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>906925</t>
+          <t>905266</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>951077</t>
+          <t>948917</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>82,21%</t>
+          <t>82,05%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>86,21%</t>
+          <t>86,01%</t>
         </is>
       </c>
     </row>
@@ -2215,12 +2215,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>91706</t>
+          <t>91814</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>128736</t>
+          <t>128460</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>16,47%</t>
+          <t>16,49%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>23,13%</t>
+          <t>23,08%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>55524</t>
+          <t>56287</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>78658</t>
+          <t>79781</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>10,3%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>14,39%</t>
+          <t>14,6%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>152168</t>
+          <t>154328</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>196320</t>
+          <t>197979</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,12 +2300,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>13,99%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>17,79%</t>
+          <t>17,95%</t>
         </is>
       </c>
     </row>
@@ -2445,12 +2445,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>290250</t>
+          <t>288647</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>313258</t>
+          <t>313583</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2460,12 +2460,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>79,87%</t>
+          <t>79,43%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>86,2%</t>
+          <t>86,29%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2480,12 +2480,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>543796</t>
+          <t>542888</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>591909</t>
+          <t>591801</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2495,12 +2495,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>89,66%</t>
+          <t>89,51%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>97,57%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2515,12 +2515,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>836044</t>
+          <t>835731</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>919809</t>
+          <t>914759</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>86,2%</t>
+          <t>86,17%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>94,84%</t>
+          <t>94,31%</t>
         </is>
       </c>
     </row>
@@ -2558,12 +2558,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>50134</t>
+          <t>49809</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>73142</t>
+          <t>74745</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2573,12 +2573,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>13,71%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>20,13%</t>
+          <t>20,57%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2593,12 +2593,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>14600</t>
+          <t>14708</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>62713</t>
+          <t>63621</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2608,12 +2608,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>50092</t>
+          <t>55142</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>133857</t>
+          <t>134170</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2643,12 +2643,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>13,83%</t>
         </is>
       </c>
     </row>
@@ -2788,12 +2788,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>240063</t>
+          <t>239511</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>257770</t>
+          <t>257809</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>85,36%</t>
+          <t>85,17%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>91,66%</t>
+          <t>91,67%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>365447</t>
+          <t>366014</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>384508</t>
+          <t>384843</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>86,49%</t>
+          <t>86,62%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>91,0%</t>
+          <t>91,08%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>612626</t>
+          <t>609492</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>637857</t>
+          <t>638174</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>87,05%</t>
+          <t>86,61%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>90,64%</t>
+          <t>90,68%</t>
         </is>
       </c>
     </row>
@@ -2901,12 +2901,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>23457</t>
+          <t>23418</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>41164</t>
+          <t>41716</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>14,83%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>38020</t>
+          <t>37685</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>57081</t>
+          <t>56514</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>13,51%</t>
+          <t>13,38%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>65898</t>
+          <t>65581</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>91129</t>
+          <t>94263</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>13,39%</t>
         </is>
       </c>
     </row>
@@ -3131,12 +3131,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2875657</t>
+          <t>2868463</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>3044662</t>
+          <t>3037284</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3146,12 +3146,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>83,6%</t>
+          <t>83,39%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>88,51%</t>
+          <t>88,3%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3166,12 +3166,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>3189337</t>
+          <t>3188872</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>3307672</t>
+          <t>3303712</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3181,12 +3181,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>87,73%</t>
+          <t>87,72%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>90,99%</t>
+          <t>90,88%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>6087588</t>
+          <t>6088937</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>6310817</t>
+          <t>6286971</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3216,12 +3216,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>86,04%</t>
+          <t>86,06%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>89,2%</t>
+          <t>88,86%</t>
         </is>
       </c>
     </row>
@@ -3244,12 +3244,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>395194</t>
+          <t>402572</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>564199</t>
+          <t>571393</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3259,12 +3259,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>11,7%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>16,61%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>327718</t>
+          <t>331678</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>446053</t>
+          <t>446518</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3294,12 +3294,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>12,28%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>764429</t>
+          <t>788275</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>987658</t>
+          <t>986309</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3329,12 +3329,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>11,14%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>13,94%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P36BPD13_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P36BPD13_2023-Edad-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>350624</t>
+          <t>357917</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>321706</t>
+          <t>334412</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>369614</t>
+          <t>375963</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>87,66%</t>
+          <t>87,77%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>80,43%</t>
+          <t>82,01%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>92,41%</t>
+          <t>92,19%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>266304</t>
+          <t>310229</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>248129</t>
+          <t>288789</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>281876</t>
+          <t>326862</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>86,15%</t>
+          <t>86,56%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>80,27%</t>
+          <t>80,58%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>91,19%</t>
+          <t>91,2%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>616928</t>
+          <t>668147</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>587692</t>
+          <t>637927</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>641183</t>
+          <t>693420</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>87,0%</t>
+          <t>87,2%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>82,88%</t>
+          <t>83,26%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>90,42%</t>
+          <t>90,5%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>49363</t>
+          <t>49876</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>30373</t>
+          <t>31830</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>78281</t>
+          <t>73381</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>19,57%</t>
+          <t>17,99%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>42812</t>
+          <t>48169</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>27240</t>
+          <t>31536</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>60987</t>
+          <t>69609</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>13,85%</t>
+          <t>13,44%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>19,73%</t>
+          <t>19,42%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>92175</t>
+          <t>98045</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>67920</t>
+          <t>72772</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>121411</t>
+          <t>128265</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>12,8%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>17,12%</t>
+          <t>16,74%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>309116</t>
+          <t>358398</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>309116</t>
+          <t>358398</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>309116</t>
+          <t>358398</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>709103</t>
+          <t>766192</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>709103</t>
+          <t>766192</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>709103</t>
+          <t>766192</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,32 +1068,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>342131</t>
+          <t>389986</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>319121</t>
+          <t>366480</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>362181</t>
+          <t>411436</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>81,07%</t>
+          <t>81,99%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>75,62%</t>
+          <t>77,05%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>85,82%</t>
+          <t>86,5%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,32 +1103,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>459897</t>
+          <t>442756</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>442921</t>
+          <t>426259</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>479024</t>
+          <t>456403</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>91,1%</t>
+          <t>89,54%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>87,74%</t>
+          <t>86,2%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>94,89%</t>
+          <t>92,3%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>802028</t>
+          <t>832742</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>773107</t>
+          <t>805002</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>834646</t>
+          <t>858926</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>86,53%</t>
+          <t>85,84%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>83,41%</t>
+          <t>82,98%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>90,05%</t>
+          <t>88,54%</t>
         </is>
       </c>
     </row>
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>79885</t>
+          <t>85667</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>59835</t>
+          <t>64217</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>102895</t>
+          <t>109173</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>18,93%</t>
+          <t>18,01%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>24,38%</t>
+          <t>22,95%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>44933</t>
+          <t>51725</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>25806</t>
+          <t>38078</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>61909</t>
+          <t>68222</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>10,46%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>13,8%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>124818</t>
+          <t>137392</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>92200</t>
+          <t>111208</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>153739</t>
+          <t>165132</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>14,16%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>11,46%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>16,59%</t>
+          <t>17,02%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>422016</t>
+          <t>475653</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>422016</t>
+          <t>475653</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>422016</t>
+          <t>475653</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>504830</t>
+          <t>494481</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>504830</t>
+          <t>494481</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>504830</t>
+          <t>494481</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>926846</t>
+          <t>970134</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>926846</t>
+          <t>970134</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>926846</t>
+          <t>970134</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>455530</t>
+          <t>531997</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>436954</t>
+          <t>511792</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>472230</t>
+          <t>549392</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>85,41%</t>
+          <t>86,13%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>81,92%</t>
+          <t>82,86%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>88,54%</t>
+          <t>88,95%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>463729</t>
+          <t>528245</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>448413</t>
+          <t>512213</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>476843</t>
+          <t>543912</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>85,88%</t>
+          <t>85,34%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>83,04%</t>
+          <t>82,75%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>88,31%</t>
+          <t>87,87%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>919259</t>
+          <t>1060242</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>897888</t>
+          <t>1035751</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>942716</t>
+          <t>1083319</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>85,64%</t>
+          <t>85,74%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>83,65%</t>
+          <t>83,76%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>87,83%</t>
+          <t>87,6%</t>
         </is>
       </c>
     </row>
@@ -1524,32 +1524,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>77838</t>
+          <t>85646</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>61138</t>
+          <t>68251</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>96414</t>
+          <t>105851</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>13,87%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>11,05%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>17,14%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1559,32 +1559,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>76262</t>
+          <t>90739</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>63148</t>
+          <t>75072</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>91578</t>
+          <t>106771</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>14,66%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>16,96%</t>
+          <t>17,25%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>154100</t>
+          <t>176385</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>130643</t>
+          <t>153308</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>175471</t>
+          <t>200876</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>14,26%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>12,4%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>16,35%</t>
+          <t>16,24%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>533368</t>
+          <t>617643</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>533368</t>
+          <t>617643</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>533368</t>
+          <t>617643</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>539991</t>
+          <t>618984</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>539991</t>
+          <t>618984</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>539991</t>
+          <t>618984</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1073359</t>
+          <t>1236627</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1073359</t>
+          <t>1236627</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1073359</t>
+          <t>1236627</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>788834</t>
+          <t>593282</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>743093</t>
+          <t>573556</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>844937</t>
+          <t>612739</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>89,32%</t>
+          <t>85,24%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>84,14%</t>
+          <t>82,41%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>95,67%</t>
+          <t>88,04%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>621135</t>
+          <t>637428</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>604485</t>
+          <t>620286</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>637243</t>
+          <t>650391</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>88,0%</t>
+          <t>87,5%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>85,64%</t>
+          <t>85,14%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>90,28%</t>
+          <t>89,28%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>1409969</t>
+          <t>1230710</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1365074</t>
+          <t>1204939</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1478491</t>
+          <t>1253680</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>88,73%</t>
+          <t>86,4%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>85,91%</t>
+          <t>84,59%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>93,04%</t>
+          <t>88,01%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>94370</t>
+          <t>102701</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>38267</t>
+          <t>83244</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>140111</t>
+          <t>122427</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>14,76%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>11,96%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>15,86%</t>
+          <t>17,59%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>84698</t>
+          <t>91092</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>68590</t>
+          <t>78129</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>101348</t>
+          <t>108234</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>10,72%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>14,86%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>179068</t>
+          <t>193792</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>110546</t>
+          <t>170822</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>223963</t>
+          <t>219563</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>14,09%</t>
+          <t>15,41%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>883204</t>
+          <t>695983</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>883204</t>
+          <t>695983</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>883204</t>
+          <t>695983</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>705833</t>
+          <t>728520</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>705833</t>
+          <t>728520</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>705833</t>
+          <t>728520</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1589037</t>
+          <t>1424502</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1589037</t>
+          <t>1424502</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1589037</t>
+          <t>1424502</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2097,32 +2097,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>448235</t>
+          <t>487811</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>428202</t>
+          <t>467496</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>464848</t>
+          <t>505879</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>80,52%</t>
+          <t>80,69%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>76,92%</t>
+          <t>77,33%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>83,51%</t>
+          <t>83,67%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,32 +2132,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>479638</t>
+          <t>529431</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>466801</t>
+          <t>516532</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>490295</t>
+          <t>542498</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>87,75%</t>
+          <t>87,22%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>85,4%</t>
+          <t>85,1%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>89,7%</t>
+          <t>89,37%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>927874</t>
+          <t>1017243</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>905266</t>
+          <t>992082</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>948917</t>
+          <t>1039249</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>84,1%</t>
+          <t>83,96%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>82,05%</t>
+          <t>81,88%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>86,01%</t>
+          <t>85,78%</t>
         </is>
       </c>
     </row>
@@ -2210,32 +2210,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>108427</t>
+          <t>116774</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>91814</t>
+          <t>98706</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>128460</t>
+          <t>137089</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>19,48%</t>
+          <t>19,31%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>16,33%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>23,08%</t>
+          <t>22,67%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,32 +2245,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>66944</t>
+          <t>77568</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>56287</t>
+          <t>64501</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>79781</t>
+          <t>90467</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>12,78%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>10,63%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>14,9%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>175371</t>
+          <t>194341</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>154328</t>
+          <t>172335</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>197979</t>
+          <t>219502</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>16,04%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>14,22%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>17,95%</t>
+          <t>18,12%</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>556662</t>
+          <t>604585</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>556662</t>
+          <t>604585</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>556662</t>
+          <t>604585</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>546582</t>
+          <t>606999</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>546582</t>
+          <t>606999</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>546582</t>
+          <t>606999</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1103245</t>
+          <t>1211584</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1103245</t>
+          <t>1211584</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1103245</t>
+          <t>1211584</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2440,32 +2440,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>302116</t>
+          <t>334910</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>288647</t>
+          <t>321093</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>313583</t>
+          <t>348122</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>83,14%</t>
+          <t>83,31%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>79,43%</t>
+          <t>79,87%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>86,29%</t>
+          <t>86,59%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,32 +2475,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>567102</t>
+          <t>393712</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>542888</t>
+          <t>383679</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>591801</t>
+          <t>403233</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>93,5%</t>
+          <t>90,05%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>89,51%</t>
+          <t>87,76%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>92,23%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,32 +2510,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>869218</t>
+          <t>728623</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>835731</t>
+          <t>711029</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>914759</t>
+          <t>742795</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>89,62%</t>
+          <t>86,82%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>86,17%</t>
+          <t>84,72%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>94,31%</t>
+          <t>88,51%</t>
         </is>
       </c>
     </row>
@@ -2553,32 +2553,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>61276</t>
+          <t>67109</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>49809</t>
+          <t>53897</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>74745</t>
+          <t>80926</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>16,86%</t>
+          <t>16,69%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>13,41%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>20,57%</t>
+          <t>20,13%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,32 +2588,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>39407</t>
+          <t>43488</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>14708</t>
+          <t>33967</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>63621</t>
+          <t>53521</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>9,95%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>12,24%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>100683</t>
+          <t>110597</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>55142</t>
+          <t>96425</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>134170</t>
+          <t>128191</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>13,18%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>11,49%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>15,28%</t>
         </is>
       </c>
     </row>
@@ -2666,17 +2666,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>363392</t>
+          <t>402019</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>363392</t>
+          <t>402019</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>363392</t>
+          <t>402019</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2701,17 +2701,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>606509</t>
+          <t>437200</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>606509</t>
+          <t>437200</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>606509</t>
+          <t>437200</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>969901</t>
+          <t>839220</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>969901</t>
+          <t>839220</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>969901</t>
+          <t>839220</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2783,32 +2783,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>249135</t>
+          <t>272472</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>239511</t>
+          <t>261527</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>257809</t>
+          <t>280843</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>88,59%</t>
+          <t>88,51%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>85,17%</t>
+          <t>84,96%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>91,67%</t>
+          <t>91,23%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,32 +2818,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>375850</t>
+          <t>409898</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>366014</t>
+          <t>398369</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>384843</t>
+          <t>419291</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>88,95%</t>
+          <t>89,0%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>86,62%</t>
+          <t>86,5%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>91,08%</t>
+          <t>91,04%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,17 +2853,17 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>624986</t>
+          <t>682370</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>609492</t>
+          <t>665660</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>638174</t>
+          <t>695610</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>86,61%</t>
+          <t>86,63%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>90,68%</t>
+          <t>90,53%</t>
         </is>
       </c>
     </row>
@@ -2896,32 +2896,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>32092</t>
+          <t>35366</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>23418</t>
+          <t>26995</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>41716</t>
+          <t>46311</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>11,49%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>15,04%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2931,32 +2931,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>46678</t>
+          <t>50637</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>37685</t>
+          <t>41244</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>56514</t>
+          <t>62166</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,17 +2966,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>78769</t>
+          <t>86003</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>65581</t>
+          <t>72763</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>94263</t>
+          <t>102713</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>13,37%</t>
         </is>
       </c>
     </row>
@@ -3009,17 +3009,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>281227</t>
+          <t>307838</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>281227</t>
+          <t>307838</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>281227</t>
+          <t>307838</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3044,17 +3044,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>422528</t>
+          <t>460535</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>422528</t>
+          <t>460535</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>422528</t>
+          <t>460535</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>703755</t>
+          <t>768373</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>703755</t>
+          <t>768373</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>703755</t>
+          <t>768373</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3126,32 +3126,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>2936605</t>
+          <t>2968376</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2868463</t>
+          <t>2919385</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>3037284</t>
+          <t>3018999</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>85,37%</t>
+          <t>84,53%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>83,39%</t>
+          <t>83,14%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>88,3%</t>
+          <t>85,97%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3161,32 +3161,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>3233657</t>
+          <t>3251699</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>3188872</t>
+          <t>3216731</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>3303712</t>
+          <t>3288283</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>88,95%</t>
+          <t>87,76%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>87,72%</t>
+          <t>86,82%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>90,88%</t>
+          <t>88,75%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,32 +3196,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>6170262</t>
+          <t>6220076</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>6088937</t>
+          <t>6159518</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>6286971</t>
+          <t>6280462</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>87,21%</t>
+          <t>86,19%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>86,06%</t>
+          <t>85,35%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>88,86%</t>
+          <t>87,03%</t>
         </is>
       </c>
     </row>
@@ -3239,32 +3239,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>503251</t>
+          <t>543139</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>402572</t>
+          <t>492516</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>571393</t>
+          <t>592130</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>15,47%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>14,03%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>16,61%</t>
+          <t>16,86%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3274,32 +3274,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>401733</t>
+          <t>453418</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>331678</t>
+          <t>416834</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>446518</t>
+          <t>488386</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>12,24%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>11,25%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>13,18%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,32 +3309,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>904984</t>
+          <t>996556</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>788275</t>
+          <t>936170</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>986309</t>
+          <t>1057114</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>13,81%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>12,97%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>14,65%</t>
         </is>
       </c>
     </row>
@@ -3352,17 +3352,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3439856</t>
+          <t>3511515</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3439856</t>
+          <t>3511515</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3439856</t>
+          <t>3511515</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3387,17 +3387,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3635390</t>
+          <t>3705117</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3635390</t>
+          <t>3705117</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3635390</t>
+          <t>3705117</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3422,17 +3422,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>7075246</t>
+          <t>7216632</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>7075246</t>
+          <t>7216632</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>7075246</t>
+          <t>7216632</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
